--- a/test/output/summary_all_videos.xlsx
+++ b/test/output/summary_all_videos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>Video</t>
   </si>
@@ -22,6 +22,9 @@
     <t>Frames</t>
   </si>
   <si>
+    <t>Mode</t>
+  </si>
+  <si>
     <t>X_Amp_mm</t>
   </si>
   <si>
@@ -71,6 +74,12 @@
   </si>
   <si>
     <t>100</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>Ellipse+Tilt</t>
   </si>
 </sst>
 </file>
@@ -428,10 +437,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -459,295 +468,328 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2">
         <v>1486</v>
       </c>
-      <c r="C2">
-        <v>0.8027709960937487</v>
+      <c r="C2" t="s">
+        <v>20</v>
       </c>
       <c r="D2">
-        <v>0.5748339843750002</v>
+        <v>0.5202213209504637</v>
       </c>
       <c r="E2">
-        <v>0.9873577779922471</v>
+        <v>0.6016920440055016</v>
       </c>
       <c r="F2">
-        <v>-8.666062030437729</v>
+        <v>0.7954014952154438</v>
       </c>
       <c r="G2">
-        <v>-10.1753462436254</v>
+        <v>-8.685258425158031</v>
       </c>
       <c r="H2">
-        <v>0.1288108070976456</v>
+        <v>-11.01473184106647</v>
       </c>
       <c r="I2">
-        <v>0.09617485162754855</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>0.1044763523043358</v>
+      </c>
+      <c r="J2">
+        <v>0.1145580547800732</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>1487</v>
       </c>
-      <c r="C3">
-        <v>0.7062276715609304</v>
+      <c r="C3" t="s">
+        <v>21</v>
       </c>
       <c r="D3">
-        <v>0.4868986043498735</v>
+        <v>0.4940804874195773</v>
       </c>
       <c r="E3">
-        <v>0.8578040423058334</v>
+        <v>0.8949064366957706</v>
       </c>
       <c r="F3">
-        <v>-8.881693563733256</v>
+        <v>1.022239237403989</v>
       </c>
       <c r="G3">
-        <v>-10.17129962621773</v>
+        <v>-0.8174098457107333</v>
       </c>
       <c r="H3">
-        <v>0.08192681882179509</v>
+        <v>-9.111950886683712</v>
       </c>
       <c r="I3">
-        <v>0.08286199243989378</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>0.08621131909617666</v>
+      </c>
+      <c r="J3">
+        <v>0.1653246526128535</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>1496</v>
       </c>
-      <c r="C4">
-        <v>0.5441894531249998</v>
+      <c r="C4" t="s">
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>0.3482484423424584</v>
+        <v>0.5182934929342831</v>
       </c>
       <c r="E4">
-        <v>0.6460798236181308</v>
+        <v>0.7543110566980686</v>
       </c>
       <c r="F4">
-        <v>-7.27143462457652</v>
+        <v>0.9152121694312072</v>
       </c>
       <c r="G4">
-        <v>-8.324321362303607</v>
+        <v>-0.803128756342355</v>
       </c>
       <c r="H4">
-        <v>0.07843720256720768</v>
+        <v>-8.953538598290102</v>
       </c>
       <c r="I4">
-        <v>0.05740135413336347</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>0.07170355025490073</v>
+      </c>
+      <c r="J4">
+        <v>0.113955120327832</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>1491</v>
       </c>
-      <c r="C5">
-        <v>0.5421862792968756</v>
+      <c r="C5" t="s">
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>0.6619738769531262</v>
+        <v>0.411346435546875</v>
       </c>
       <c r="E5">
-        <v>0.8556724695969493</v>
+        <v>0.5668460621553305</v>
       </c>
       <c r="F5">
-        <v>-8.704628018242262</v>
+        <v>0.7003715786767223</v>
       </c>
       <c r="G5">
-        <v>-10.34485561694385</v>
+        <v>-0.6889793574868308</v>
       </c>
       <c r="H5">
-        <v>0.0847413862997911</v>
+        <v>-8.856888831509853</v>
       </c>
       <c r="I5">
-        <v>0.07160004991690785</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>0.07320177273310441</v>
+      </c>
+      <c r="J5">
+        <v>0.107511803677444</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>1495</v>
       </c>
-      <c r="C6">
-        <v>0.6434692382812514</v>
+      <c r="C6" t="s">
+        <v>21</v>
       </c>
       <c r="D6">
-        <v>0.5380261230468752</v>
+        <v>0.4416503906250001</v>
       </c>
       <c r="E6">
-        <v>0.8387638342794145</v>
+        <v>0.5744341681985284</v>
       </c>
       <c r="F6">
-        <v>-8.744699531661526</v>
+        <v>0.7245893189477405</v>
       </c>
       <c r="G6">
-        <v>-10.2862950439943</v>
+        <v>-0.7275207424814465</v>
       </c>
       <c r="H6">
-        <v>0.09341830194450408</v>
+        <v>-8.915220389363709</v>
       </c>
       <c r="I6">
-        <v>0.07241524855516021</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>0.0610418762586484</v>
+      </c>
+      <c r="J6">
+        <v>0.09039594536771627</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>1495</v>
       </c>
-      <c r="C7">
-        <v>0.4881043221786436</v>
+      <c r="C7" t="s">
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>0.3208660172064788</v>
+        <v>0.4654379451976103</v>
       </c>
       <c r="E7">
-        <v>0.5841239854067127</v>
+        <v>0.466463874368106</v>
       </c>
       <c r="F7">
-        <v>-7.08143187074852</v>
+        <v>0.6589544953335382</v>
       </c>
       <c r="G7">
-        <v>-8.24375066813467</v>
+        <v>-0.7615468736695444</v>
       </c>
       <c r="H7">
-        <v>0.07312462297203776</v>
+        <v>-8.762274095209944</v>
       </c>
       <c r="I7">
-        <v>0.05186533813991943</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>0.07328898758959103</v>
+      </c>
+      <c r="J7">
+        <v>0.08092439421140236</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>1496</v>
       </c>
-      <c r="C8">
-        <v>0.6723889160156257</v>
+      <c r="C8" t="s">
+        <v>21</v>
       </c>
       <c r="D8">
-        <v>0.4288806152343752</v>
+        <v>0.4476713292738971</v>
       </c>
       <c r="E8">
-        <v>0.7975245679629464</v>
+        <v>0.5595810834099265</v>
       </c>
       <c r="F8">
-        <v>-8.787674449524248</v>
+        <v>0.7166174767364282</v>
       </c>
       <c r="G8">
-        <v>-10.13711415748637</v>
+        <v>-0.7902838000724414</v>
       </c>
       <c r="H8">
-        <v>0.09629551794886294</v>
+        <v>-8.891117796757189</v>
       </c>
       <c r="I8">
-        <v>0.07012826188264064</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>0.0672673910572299</v>
+      </c>
+      <c r="J8">
+        <v>0.07990413811789694</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>1496</v>
       </c>
-      <c r="C9">
-        <v>0.6121422552293346</v>
+      <c r="C9" t="s">
+        <v>21</v>
       </c>
       <c r="D9">
-        <v>0.3043744487147177</v>
+        <v>0.4423801197725185</v>
       </c>
       <c r="E9">
-        <v>0.683638753778371</v>
+        <v>0.7454600614659919</v>
       </c>
       <c r="F9">
-        <v>-7.129043865969954</v>
+        <v>0.8668395893190551</v>
       </c>
       <c r="G9">
-        <v>-8.212748411248668</v>
+        <v>-0.7903126352958743</v>
       </c>
       <c r="H9">
-        <v>0.1101438144808986</v>
+        <v>-8.981821519197101</v>
       </c>
       <c r="I9">
-        <v>0.04757498449301455</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>0.07244519784986851</v>
+      </c>
+      <c r="J9">
+        <v>0.09545820134535411</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>1487</v>
       </c>
-      <c r="C10">
-        <v>1.881934381300382</v>
+      <c r="C10" t="s">
+        <v>21</v>
       </c>
       <c r="D10">
-        <v>1.405299032888042</v>
+        <v>0.4331036735983456</v>
       </c>
       <c r="E10">
-        <v>2.348732080795193</v>
+        <v>0.4244627111098347</v>
       </c>
       <c r="F10">
-        <v>-12.87071941927272</v>
+        <v>0.6064217882028096</v>
       </c>
       <c r="G10">
-        <v>-16.62659191060641</v>
+        <v>-0.350681701960996</v>
       </c>
       <c r="H10">
-        <v>0.4245906573222096</v>
+        <v>-8.715845645419384</v>
       </c>
       <c r="I10">
-        <v>0.2798137960893069</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>0.08618655509177378</v>
+      </c>
+      <c r="J10">
+        <v>0.06390900910259444</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>1485</v>
       </c>
-      <c r="C11">
-        <v>1.791912841796875</v>
+      <c r="C11" t="s">
+        <v>21</v>
       </c>
       <c r="D11">
-        <v>1.504394531250002</v>
+        <v>0.4072911879595589</v>
       </c>
       <c r="E11">
-        <v>2.339691120265977</v>
+        <v>0.5649072983685659</v>
       </c>
       <c r="F11">
-        <v>-13.62857730143229</v>
+        <v>0.6964239854711932</v>
       </c>
       <c r="G11">
-        <v>-17.09758230317498</v>
+        <v>-0.2703239799476825</v>
       </c>
       <c r="H11">
-        <v>0.3555554813161669</v>
+        <v>-8.700233037086164</v>
       </c>
       <c r="I11">
-        <v>0.2801733901156572</v>
+        <v>0.06939297696938147</v>
+      </c>
+      <c r="J11">
+        <v>0.09433756266388707</v>
       </c>
     </row>
   </sheetData>
